--- a/task190/golden/review_placement_2027.xlsx
+++ b/task190/golden/review_placement_2027.xlsx
@@ -508,7 +508,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="5">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>7</v>
@@ -519,7 +519,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="5">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>7</v>
@@ -530,7 +530,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="5">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>7</v>
@@ -541,7 +541,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="5">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>11</v>
@@ -552,7 +552,7 @@
         <v>12</v>
       </c>
       <c r="B10" s="5">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>11</v>
@@ -563,7 +563,7 @@
         <v>13</v>
       </c>
       <c r="B11" s="5">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>11</v>
@@ -585,7 +585,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>7</v>
